--- a/evaluate.xlsx
+++ b/evaluate.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B120"/>
+  <dimension ref="A1:B272"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -431,1426 +431,3250 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>600015</t>
+          <t>600008</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>华夏银行</t>
+          <t>首创环保</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>600026</t>
+          <t>600011</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>中远海能</t>
+          <t>华能国际</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>600098</t>
+          <t>600012</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>广州发展</t>
+          <t>皖通高速</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>600108</t>
+          <t>600016</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>亚盛集团</t>
+          <t>民生银行</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>600130</t>
+          <t>600017</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>*ST波导</t>
+          <t>日照港</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>600131</t>
+          <t>600023</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>国网信通</t>
+          <t>浙能电力</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>600152</t>
+          <t>600025</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>维科技术</t>
+          <t>华能水电</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>600158</t>
+          <t>600027</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>中体产业</t>
+          <t>华电国际</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>600163</t>
+          <t>600032</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>中闽能源</t>
+          <t>浙江新能</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>600168</t>
+          <t>600035</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>武汉控股</t>
+          <t>楚天高速</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>600193</t>
+          <t>600051</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>*ST创兴</t>
+          <t>宁波联合</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>600202</t>
+          <t>600063</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>哈空调</t>
+          <t>皖维高新</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>600227</t>
+          <t>600075</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>赤天化</t>
+          <t>新疆天业</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>600233</t>
+          <t>600098</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>圆通速递</t>
+          <t>广州发展</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>600237</t>
+          <t>600101</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>铜峰电子</t>
+          <t>明星电力</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>600241</t>
+          <t>600108</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>时代万恒</t>
+          <t>亚盛集团</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>600261</t>
+          <t>600110</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>阳光照明</t>
+          <t>诺德股份</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>600289</t>
+          <t>600116</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>ST信通</t>
+          <t>三峡水利</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>600310</t>
+          <t>600121</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>广西能源</t>
+          <t>郑州煤电</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>600361</t>
+          <t>600123</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>创新新材</t>
+          <t>兰花科创</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>600379</t>
+          <t>600126</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>宝光股份</t>
+          <t>杭钢股份</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>600396</t>
+          <t>600130</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>华电辽能</t>
+          <t>*ST波导</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>600410</t>
+          <t>600131</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>华胜天成</t>
+          <t>国网信通</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>600475</t>
+          <t>600132</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>华光环能</t>
+          <t>重庆啤酒</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>600483</t>
+          <t>600149</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>福能股份</t>
+          <t>廊坊发展</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>600498</t>
+          <t>600157</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>烽火通信</t>
+          <t>永泰能源</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>600502</t>
+          <t>600158</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>安徽建工</t>
+          <t>中体产业</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>600509</t>
+          <t>600163</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>天富能源</t>
+          <t>中闽能源</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>600511</t>
+          <t>600168</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>国药股份</t>
+          <t>武汉控股</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>600516</t>
+          <t>600169</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>方大炭素</t>
+          <t>ST太重</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>600525</t>
+          <t>600172</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>ST长园</t>
+          <t>黄河旋风</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>600528</t>
+          <t>600180</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>中铁工业</t>
+          <t>瑞茂通</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>600545</t>
+          <t>600188</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>卓郎智能</t>
+          <t>兖矿能源</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>600558</t>
+          <t>600202</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>大西洋</t>
+          <t>哈空调</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>600568</t>
+          <t>600216</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>ST中珠</t>
+          <t>浙江医药</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>600645</t>
+          <t>600227</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>中源协和</t>
+          <t>赤天化</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>600666</t>
+          <t>600236</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>奥瑞德</t>
+          <t>桂冠电力</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>600710</t>
+          <t>600237</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>苏美达</t>
+          <t>铜峰电子</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>600719</t>
+          <t>600241</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>大连热电</t>
+          <t>时代万恒</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>600725</t>
+          <t>600251</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>云维股份</t>
+          <t>冠农股份</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>600726</t>
+          <t>600256</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>华电能源</t>
+          <t>广汇能源</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>600769</t>
+          <t>600261</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>祥龙电业</t>
+          <t>阳光照明</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>600775</t>
+          <t>600268</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>南京熊猫</t>
+          <t>国电南自</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>600780</t>
+          <t>600283</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>通宝能源</t>
+          <t>钱江水利</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>600784</t>
+          <t>600289</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>鲁银投资</t>
+          <t>ST信通</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>600808</t>
+          <t>600299</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>马钢股份</t>
+          <t>安迪苏</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>600821</t>
+          <t>600310</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>金开新能</t>
+          <t>广西能源</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>600851</t>
+          <t>600312</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>海欣股份</t>
+          <t>平高电气</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>600860</t>
+          <t>600318</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>京城股份</t>
+          <t>新力金融</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>600867</t>
+          <t>600319</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>通化东宝</t>
+          <t>亚星化学</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>600905</t>
+          <t>600328</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>三峡能源</t>
+          <t>中盐化工</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>601016</t>
+          <t>600365</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>节能风电</t>
+          <t>ST通葡</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>601033</t>
+          <t>600367</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>永兴股份</t>
+          <t>红星发展</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>601218</t>
+          <t>600368</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>吉鑫科技</t>
+          <t>五洲交通</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>601368</t>
+          <t>600377</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>绿城水务</t>
+          <t>宁沪高速</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>601369</t>
+          <t>600379</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>陕鼓动力</t>
+          <t>宝光股份</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>601567</t>
+          <t>600389</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>三星医疗</t>
+          <t>江山股份</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>601611</t>
+          <t>600396</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>中国核建</t>
+          <t>华电辽能</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>601616</t>
+          <t>600405</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>广电电气</t>
+          <t>动力源</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>601618</t>
+          <t>600406</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>中国中冶</t>
+          <t>国电南瑞</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>601669</t>
+          <t>600409</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>中国电建</t>
+          <t>三友化工</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>601778</t>
+          <t>600410</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>晶科科技</t>
+          <t>华胜天成</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>601838</t>
+          <t>600423</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>成都银行</t>
+          <t>柳化股份</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>601868</t>
+          <t>600426</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>中国能建</t>
+          <t>华鲁恒升</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>601872</t>
+          <t>600433</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>招商轮船</t>
+          <t>冠豪高新</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>601877</t>
+          <t>600452</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>正泰电器</t>
+          <t>涪陵电力</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>601975</t>
+          <t>600468</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>招商南油</t>
+          <t>百利电气</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>603007</t>
+          <t>600470</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>*ST花王</t>
+          <t>六国化工</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>603011</t>
+          <t>600475</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>合锻智能</t>
+          <t>华光环能</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>603021</t>
+          <t>600482</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>ST华鹏</t>
+          <t>中国动力</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>603045</t>
+          <t>600483</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>福达合金</t>
+          <t>福能股份</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>603050</t>
+          <t>600486</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>科林电气</t>
+          <t>扬农化工</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>603097</t>
+          <t>600500</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>江苏华辰</t>
+          <t>中化国际</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>603098</t>
+          <t>600502</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>森特股份</t>
+          <t>安徽建工</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>603110</t>
+          <t>600508</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>东方材料</t>
+          <t>上海能源</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>603118</t>
+          <t>600509</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>共进股份</t>
+          <t>天富能源</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>603138</t>
+          <t>600512</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>海量数据</t>
+          <t>腾达建设</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>603165</t>
+          <t>600513</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>荣晟环保</t>
+          <t>联环药业</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>603175</t>
+          <t>600516</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>超颖电子</t>
+          <t>方大炭素</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>603187</t>
+          <t>600527</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>海容冷链</t>
+          <t>江南高纤</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>603203</t>
+          <t>600539</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>快克智能</t>
+          <t>狮头股份</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>603218</t>
+          <t>600545</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>日月股份</t>
+          <t>卓郎智能</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>603220</t>
+          <t>600546</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>中贝通信</t>
+          <t>山煤国际</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>603268</t>
+          <t>600563</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>*ST松发</t>
+          <t>法拉电子</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>603269</t>
+          <t>600567</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>海鸥股份</t>
+          <t>山鹰国际</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>603309</t>
+          <t>600568</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>维力医疗</t>
+          <t>ST中珠</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>603318</t>
+          <t>600575</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>水发燃气</t>
+          <t>淮河能源</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>603333</t>
+          <t>600578</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>尚纬股份</t>
+          <t>京能电力</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>603356</t>
+          <t>600582</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>华菱精工</t>
+          <t>天地科技</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>603421</t>
+          <t>600598</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>鼎信通讯</t>
+          <t>北大荒</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>603477</t>
+          <t>600600</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>巨星农牧</t>
+          <t>青岛啤酒</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>603489</t>
+          <t>600603</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>八方股份</t>
+          <t>广汇物流</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>603496</t>
+          <t>600617</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>恒为科技</t>
+          <t>国新能源</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>603530</t>
+          <t>600623</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>神马电力</t>
+          <t>华谊集团</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>603538</t>
+          <t>600629</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>美诺华</t>
+          <t>华建集团</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>603556</t>
+          <t>600642</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>海兴电力</t>
+          <t>申能股份</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>603577</t>
+          <t>600644</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>汇金通</t>
+          <t>乐山电力</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>603588</t>
+          <t>600645</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>高能环境</t>
+          <t>中源协和</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>603688</t>
+          <t>600666</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>石英股份</t>
+          <t>奥瑞德</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>603701</t>
+          <t>600673</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>德宏股份</t>
+          <t>东阳光</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>603810</t>
+          <t>600674</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>丰山集团</t>
+          <t>川投能源</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>603863</t>
+          <t>600681</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>松炀资源</t>
+          <t>百川能源</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>603871</t>
+          <t>600683</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>嘉友国际</t>
+          <t>京投发展</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>603880</t>
+          <t>600691</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>南卫股份</t>
+          <t>潞化科技</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>603887</t>
+          <t>600714</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>城地香江</t>
+          <t>金瑞矿业</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>603897</t>
+          <t>600719</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>长城科技</t>
+          <t>大连热电</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>603912</t>
+          <t>600722</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>佳力图</t>
+          <t>金牛化工</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>603936</t>
+          <t>600726</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>博敏电子</t>
+          <t>华电能源</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>603985</t>
+          <t>600732</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>恒润股份</t>
+          <t>爱旭股份</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>603991</t>
+          <t>600735</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>至正股份</t>
+          <t>ST新华锦</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>605005</t>
+          <t>600744</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>合兴股份</t>
+          <t>华银电力</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>605007</t>
+          <t>600746</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>五洲特纸</t>
+          <t>江苏索普</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>605058</t>
+          <t>600753</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>澳弘电子</t>
+          <t>*ST海钦</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>605196</t>
+          <t>600758</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>华通线缆</t>
+          <t>辽宁能源</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>605258</t>
+          <t>600759</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>协和电子</t>
+          <t>洲际油气</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>605298</t>
+          <t>600769</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>必得科技</t>
+          <t>祥龙电业</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>605366</t>
+          <t>600773</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>宏柏新材</t>
+          <t>西藏城投</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>605377</t>
+          <t>600775</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>华旺科技</t>
+          <t>南京熊猫</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
+          <t>600780</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>通宝能源</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>600784</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>鲁银投资</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>600794</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>保税科技</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>600795</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>国电电力</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>600803</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>新奥股份</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>600821</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>金开新能</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>600844</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>金煤科技</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>600851</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>海欣股份</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>600854</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>春兰股份</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>600866</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>星湖科技</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>600873</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>梅花生物</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>600874</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>创业环保</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>600886</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>国投电力</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>600900</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>长江电力</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>600905</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>三峡能源</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>600919</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>江苏银行</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>600925</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>苏能股份</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>600926</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>杭州银行</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>600929</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>雪天盐业</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>600930</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>华电新能</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>600935</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>华塑股份</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>600938</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>中国海油</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>600956</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>新天绿能</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>600971</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>恒源煤电</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>600979</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>广安爱众</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>600982</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>宁波能源</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>600985</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>淮北矿业</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>600989</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>宝丰能源</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>600995</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>南网储能</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>600997</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>开滦股份</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>601001</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>晋控煤业</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>601006</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>大秦铁路</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>601016</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>节能风电</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>601026</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>道生天合</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>601033</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>永兴股份</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>601065</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>江盐集团</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>601077</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>渝农商行</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>601088</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>中国神华</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>601101</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>昊华能源</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>601117</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>中国化学</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>601118</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>海南橡胶</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>601139</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>深圳燃气</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>601158</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>重庆水务</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>601169</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>北京银行</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>601179</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>中国西电</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>601200</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>上海环境</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>601216</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>君正集团</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>601218</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>吉鑫科技</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>601222</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>林洋能源</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>601225</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>陕西煤业</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>601330</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>绿色动力</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>601368</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>绿城水务</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>601369</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>陕鼓动力</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>601518</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>吉林高速</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>601567</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>三星医疗</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>601568</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>北元集团</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>601616</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>广电电气</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>601699</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>潞安环能</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>601727</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>上海电气</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>601778</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>晶科科技</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>601789</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>宁波建工</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>601868</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>中国能建</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>601877</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>正泰电器</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>601880</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>辽港股份</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>601882</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>海天精工</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>601898</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>中煤能源</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>601908</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>京运通</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>601916</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>浙商银行</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>601918</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>新集能源</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>601952</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>苏垦农发</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>601969</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>海南矿业</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>601985</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>中国核电</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>601991</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>大唐发电</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>603007</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>*ST花王</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>603017</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>中衡设计</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>603050</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>科林电气</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>603055</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>台华新材</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>603056</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>德邦股份</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>603063</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>禾望电气</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>603070</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>万控智造</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>603071</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>物产环能</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>603077</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>和邦生物</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>603093</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>南华期货</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>603105</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>芯能科技</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>603110</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>东方材料</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>603113</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>金能科技</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>603118</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>共进股份</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>603123</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>翠微股份</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>603158</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>腾龙股份</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>603201</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>常润股份</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>603203</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>快克智能</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>603218</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>日月股份</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>603220</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>中贝通信</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>603226</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>菲林格尔</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>603235</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>天新药业</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>603269</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>海鸥股份</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>603289</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>泰瑞机器</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>603299</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>苏盐井神</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>603316</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>诚邦股份</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>603318</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>水发燃气</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>603333</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>尚纬股份</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>603356</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>华菱精工</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>603363</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>傲农生物</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>603393</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>新天然气</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>603421</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>鼎信通讯</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>603477</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>巨星农牧</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>603489</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>八方股份</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>603507</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>振江股份</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>603557</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>ST起步</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>603588</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>高能环境</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>603606</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>东方电缆</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>603610</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>麒盛科技</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>603628</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>清源股份</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>603688</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>石英股份</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>603693</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>江苏新能</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>603739</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>蔚蓝生物</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>603757</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>大元泵业</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>603778</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>国晟科技</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>603803</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>瑞斯康达</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>603817</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>海峡环保</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>603819</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>神力股份</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>603826</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>坤彩科技</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>603829</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>洛凯股份</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>603838</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>*ST四通</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>603843</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>*ST正平</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>603856</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>东宏股份</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>603871</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>嘉友国际</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>603876</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>鼎胜新材</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>603880</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>南卫股份</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>603887</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>城地香江</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>603897</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>长城科技</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>603912</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>佳力图</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>603936</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>博敏电子</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>603950</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>长源东谷</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>603985</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>恒润股份</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>603991</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>至正股份</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>605005</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>合兴股份</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>605007</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>五洲特纸</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>605011</t>
+        </is>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>杭州热电</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>605028</t>
+        </is>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>世茂能源</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>605117</t>
+        </is>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>德业股份</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>605162</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>新中港</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>605183</t>
+        </is>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>确成股份</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>605196</t>
+        </is>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>华通线缆</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>605258</t>
+        </is>
+      </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>协和电子</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>605268</t>
+        </is>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>王力安防</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>605286</t>
+        </is>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>同力天启</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>605296</t>
+        </is>
+      </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>神农集团</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>605298</t>
+        </is>
+      </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>必得科技</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>605299</t>
+        </is>
+      </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>舒华体育</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>605368</t>
+        </is>
+      </c>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>蓝天燃气</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>605377</t>
+        </is>
+      </c>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>华旺科技</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
           <t>605399</t>
         </is>
       </c>
-      <c r="B120" t="inlineStr">
+      <c r="B272" t="inlineStr">
         <is>
           <t>晨光新材</t>
         </is>
